--- a/디씨씨이엔티_연재처별_작품현황.xlsx
+++ b/디씨씨이엔티_연재처별_작품현황.xlsx
@@ -211,8 +211,10 @@
   <commentList>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>미수집: page.kakao.com 접근이 네트워크 정책으로 차단되어 카카오페이지 작품별 키워드/태그를 수집하지 못했습니다.
-주의: 카카오웹툰 시트의 태그는 카카오웹툰 자체 분류 체계이므로 카카오페이지 태그와 동일하지 않습니다. 그대로 옮겨 쓰지 마세요.</t>
+        <t>카카오페이지 작품 키워드(해시태그).
+출처: kakaopage-tracker.vercel.app works.json (카카오페이지 수집 데이터)
+트래커 수록분 19건만 기입, 미수록 24건은 공백입니다.
+주의: 카카오웹툰 시트의 태그와는 다른 체계입니다.</t>
       </text>
     </comment>
     <comment ref="S1" authorId="0" shapeId="0">
@@ -225,8 +227,16 @@
     </comment>
     <comment ref="U1" authorId="0" shapeId="0">
       <text>
-        <t>미수집: kakaopage-tracker.vercel.app 접근이 네트워크 정책으로 차단되어 일간/주간/월간 순위 추이를 수집하지 못했습니다.
-기준일(X열)에는 순위 집계 기준 날짜를, 출처(Y열)에는 조회한 URL을 기입하세요.</t>
+        <t>카카오페이지 웹툰 랭킹 TOP 300 기준.
+U~W열 = 2026-08-21 시점 순위, Z~AB열 = 2026-08-09~2026-08-21 일자별 추이.
+TOP 300에 들지 못한 작품은 공백입니다(순위 없음).
+출처: https://kakaopage-tracker.vercel.app/ (웹툰 TOP 300)</t>
+      </text>
+    </comment>
+    <comment ref="AD1" authorId="0" shapeId="0">
+      <text>
+        <t>원작 웹소설의 출판사(CP).
+카카오페이지 웹소설판이 트래커에 함께 수록된 건만 확보되어 있고, 나머지는 공백입니다.</t>
       </text>
     </comment>
   </commentList>
@@ -4188,7 +4198,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>네트워크 정책상 차단 - 일간/주간/월간 순위 추이 수집 불가</t>
+          <t>수집 완료 - 웹툰 랭킹 일간/주간/월간, 집계기간 2026-08-09~2026-08-21 (13일). 43건 중 11건이 TOP 300 진입, 나머지는 순위 없음(공백)</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y44"/>
+  <dimension ref="A1:AD44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4244,6 +4254,11 @@
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="34" customWidth="1" min="25" max="25"/>
+    <col width="52" customWidth="1" min="26" max="26"/>
+    <col width="52" customWidth="1" min="27" max="27"/>
+    <col width="52" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="30" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4372,6 +4387,31 @@
           <t>순위 출처</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>일간 순위 추이</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>주간 순위 추이</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>월간 순위 추이</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>웹소설 원작 ID</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>웹소설 출판사</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -4412,7 +4452,11 @@
           <t>웹툰 &gt; 드라마</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>#힐링물 #현대물 #성장물 #배우 #남주중심 #고퀄리티 #이야기중심</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>전체 이용가</t>
@@ -4457,14 +4501,51 @@
       </c>
       <c r="T2" s="5" t="inlineStr">
         <is>
-          <t>카카오페이지 웹소설 content/57109925 (원작: 테헤)</t>
+          <t>카카오페이지 웹소설 content/57109925 (동일작품 웹소설판 확인)</t>
         </is>
       </c>
       <c r="U2" s="4" t="n"/>
-      <c r="V2" s="4" t="n"/>
-      <c r="W2" s="4" t="n"/>
-      <c r="X2" s="4" t="n"/>
-      <c r="Y2" s="4" t="n"/>
+      <c r="V2" s="4" t="n">
+        <v>232</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="X2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>https://kakaopage-tracker.vercel.app/ (웹툰 TOP 300)</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="inlineStr">
+        <is>
+          <t>08/09 222위 · 08/10 119위 · 08/11 193위 · 08/12 262위 · 08/16 283위 · 08/17 101위 · 08/18 196위</t>
+        </is>
+      </c>
+      <c r="AA2" s="5" t="inlineStr">
+        <is>
+          <t>08/09 127위 · 08/10 176위 · 08/11 190위 · 08/12 217위 · 08/13 221위 · 08/14 226위 · 08/15 230위 · 08/16 235위 · 08/17 224위 · 08/18 230위 · 08/19 230위 · 08/20 232위 · 08/21 232위</t>
+        </is>
+      </c>
+      <c r="AB2" s="5" t="inlineStr">
+        <is>
+          <t>08/09 31위 · 08/10 31위 · 08/11 31위 · 08/12 32위 · 08/13 31위 · 08/14 31위 · 08/15 31위 · 08/16 32위 · 08/17 37위 · 08/18 41위 · 08/19 80위 · 08/20 109위 · 08/21 145위</t>
+        </is>
+      </c>
+      <c r="AC2" s="5" t="inlineStr">
+        <is>
+          <t>57109925</t>
+        </is>
+      </c>
+      <c r="AD2" s="5" t="inlineStr">
+        <is>
+          <t>브리드 / A-LIST</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -4505,7 +4586,11 @@
           <t>웹툰 &gt; 판타지</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>#게임 #빙의 #먼치킨 #시스템 #고인물 #검사 #마검사 #이종족 #만능 #이능력 #성직자 #마법사 #착각</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>전체 이용가</t>
@@ -4550,14 +4635,51 @@
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>카카오페이지 웹소설 content/58982133 (원작: 해인설)</t>
+          <t>카카오페이지 웹소설 content/58982133 (동일작품 웹소설판 확인)</t>
         </is>
       </c>
       <c r="U3" s="4" t="n"/>
-      <c r="V3" s="4" t="n"/>
-      <c r="W3" s="4" t="n"/>
-      <c r="X3" s="4" t="n"/>
-      <c r="Y3" s="4" t="n"/>
+      <c r="V3" s="4" t="n">
+        <v>286</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>https://kakaopage-tracker.vercel.app/ (웹툰 TOP 300)</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr">
+        <is>
+          <t>08/12 189위 · 08/13 124위 · 08/14 244위 · 08/19 253위 · 08/20 134위</t>
+        </is>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
+          <t>08/09 231위 · 08/10 230위 · 08/11 237위 · 08/12 242위 · 08/13 250위 · 08/14 250위 · 08/15 251위 · 08/16 247위 · 08/17 253위 · 08/18 258위 · 08/19 268위 · 08/20 275위 · 08/21 286위</t>
+        </is>
+      </c>
+      <c r="AB3" s="5" t="inlineStr">
+        <is>
+          <t>08/09 27위 · 08/10 26위 · 08/11 26위 · 08/12 27위 · 08/13 27위 · 08/14 29위 · 08/15 77위 · 08/16 109위 · 08/17 131위 · 08/18 151위 · 08/19 162위 · 08/20 169위 · 08/21 181위</t>
+        </is>
+      </c>
+      <c r="AC3" s="5" t="inlineStr">
+        <is>
+          <t>58982133</t>
+        </is>
+      </c>
+      <c r="AD3" s="5" t="inlineStr">
+        <is>
+          <t>제이플미디어</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -4598,7 +4720,11 @@
           <t>웹툰 &gt; 로판</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>#로맨스판타지 #성장물 #시한부 #영혼체인지 #계략남 #까칠남 #능력남 #계략녀 #외유내강 #힐링물</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>전체 이용가</t>
@@ -4643,14 +4769,45 @@
       </c>
       <c r="T4" s="5" t="inlineStr">
         <is>
-          <t>카카오페이지 웹소설 content/65077800 (원작: 유예랑)</t>
+          <t>카카오페이지 웹소설 content/65077800 (동일작품 웹소설판 확인)</t>
         </is>
       </c>
       <c r="U4" s="4" t="n"/>
       <c r="V4" s="4" t="n"/>
-      <c r="W4" s="4" t="n"/>
-      <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="4" t="n"/>
+      <c r="W4" s="4" t="n">
+        <v>202</v>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>https://kakaopage-tracker.vercel.app/ (웹툰 TOP 300)</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr">
+        <is>
+          <t>08/12 160위 · 08/13 85위 · 08/14 197위 · 08/15 255위</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="inlineStr">
+        <is>
+          <t>08/09 166위 · 08/10 174위 · 08/11 168위 · 08/12 181위 · 08/13 194위 · 08/14 204위 · 08/15 204위 · 08/16 204위 · 08/17 194위 · 08/18 202위 · 08/19 234위</t>
+        </is>
+      </c>
+      <c r="AB4" s="5" t="inlineStr">
+        <is>
+          <t>08/09 142위 · 08/10 144위 · 08/11 146위 · 08/12 151위 · 08/13 148위 · 08/14 149위 · 08/15 173위 · 08/16 184위 · 08/17 188위 · 08/18 190위 · 08/19 195위 · 08/20 195위 · 08/21 202위</t>
+        </is>
+      </c>
+      <c r="AC4" s="5" t="inlineStr">
+        <is>
+          <t>65077800</t>
+        </is>
+      </c>
+      <c r="AD4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -4691,7 +4848,11 @@
           <t>웹툰 &gt; 판타지</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>#차원이동 #귀환 #먼치킨 #고인물 #네크로맨서 #성장 #천재 #하렘 #레이드 #방송</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>15세 이용가</t>
@@ -4736,14 +4897,31 @@
       </c>
       <c r="T5" s="5" t="inlineStr">
         <is>
-          <t>카카오페이지 웹소설 content/63949783 (원작: 신채화)</t>
+          <t>카카오페이지 웹소설 content/63949783 (동일작품 웹소설판 확인)</t>
         </is>
       </c>
       <c r="U5" s="4" t="n"/>
       <c r="V5" s="4" t="n"/>
       <c r="W5" s="4" t="n"/>
       <c r="X5" s="4" t="n"/>
-      <c r="Y5" s="4" t="n"/>
+      <c r="Y5" s="5" t="inlineStr">
+        <is>
+          <t>https://kakaopage-tracker.vercel.app/ (웹툰 TOP 300)</t>
+        </is>
+      </c>
+      <c r="Z5" s="5" t="inlineStr">
+        <is>
+          <t>08/12 277위 · 08/19 287위</t>
+        </is>
+      </c>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
+      <c r="AC5" s="5" t="inlineStr">
+        <is>
+          <t>63949783</t>
+        </is>
+      </c>
+      <c r="AD5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -4784,7 +4962,11 @@
           <t>웹툰 &gt; 로맨스</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>#현대로맨스 #복수물 #성장물 #사내연애 #오피스물 #트라우마 #까칠남 #상처남 #순정남 #능력남 #츤데레남 #능력녀 #외유내강 #사이다녀 #로맨틱코미디</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>전체 이용가</t>
@@ -4829,14 +5011,23 @@
       </c>
       <c r="T6" s="5" t="inlineStr">
         <is>
-          <t>카카오페이지 웹소설 content/56203718 (원작: 민지안)</t>
+          <t>카카오페이지 웹소설 content/56203718 (동일작품 웹소설판 확인)</t>
         </is>
       </c>
       <c r="U6" s="4" t="n"/>
       <c r="V6" s="4" t="n"/>
       <c r="W6" s="4" t="n"/>
       <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="4" t="n"/>
+      <c r="Y6" s="5" t="n"/>
+      <c r="Z6" s="5" t="n"/>
+      <c r="AA6" s="5" t="n"/>
+      <c r="AB6" s="5" t="n"/>
+      <c r="AC6" s="5" t="inlineStr">
+        <is>
+          <t>56203718</t>
+        </is>
+      </c>
+      <c r="AD6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -4877,7 +5068,11 @@
           <t>웹툰 &gt; 로판</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>#로맨스판타지 #가상시대물 #신화물 #운명 #인외존재 #초월적존재 #후회남 #무심녀</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>15세 이용가</t>
@@ -4922,14 +5117,49 @@
       </c>
       <c r="T7" s="5" t="inlineStr">
         <is>
-          <t>카카오페이지 웹소설 content/57045319 (원작: 삼족섬)</t>
-        </is>
-      </c>
-      <c r="U7" s="4" t="n"/>
-      <c r="V7" s="4" t="n"/>
-      <c r="W7" s="4" t="n"/>
-      <c r="X7" s="4" t="n"/>
-      <c r="Y7" s="4" t="n"/>
+          <t>카카오페이지 웹소설 content/67961660 (동일작품 웹소설판 확인)</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="W7" s="4" t="n">
+        <v>177</v>
+      </c>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y7" s="5" t="inlineStr">
+        <is>
+          <t>https://kakaopage-tracker.vercel.app/ (웹툰 TOP 300)</t>
+        </is>
+      </c>
+      <c r="Z7" s="5" t="inlineStr">
+        <is>
+          <t>08/15 47위 · 08/16 49위 · 08/17 67위 · 08/18 82위 · 08/19 87위 · 08/20 111위 · 08/21 108위</t>
+        </is>
+      </c>
+      <c r="AA7" s="5" t="inlineStr">
+        <is>
+          <t>08/15 160위 · 08/16 132위 · 08/17 106위 · 08/18 98위 · 08/19 89위 · 08/20 81위 · 08/21 75위</t>
+        </is>
+      </c>
+      <c r="AB7" s="5" t="inlineStr">
+        <is>
+          <t>08/15 272위 · 08/16 230위 · 08/17 208위 · 08/18 198위 · 08/19 191위 · 08/20 183위 · 08/21 177위</t>
+        </is>
+      </c>
+      <c r="AC7" s="5" t="inlineStr">
+        <is>
+          <t>67961660</t>
+        </is>
+      </c>
+      <c r="AD7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -4970,7 +5200,11 @@
           <t>웹툰 &gt; 판타지</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>#정통 #전쟁 #먼치킨 #성장 #이종족 #복수</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>15세 이용가</t>
@@ -5015,14 +5249,31 @@
       </c>
       <c r="T8" s="5" t="inlineStr">
         <is>
-          <t>카카오페이지 웹소설 content/46742689 (원작: 김정률)</t>
+          <t>카카오페이지 웹소설 content/46742689 (동일작품 웹소설판 확인)</t>
         </is>
       </c>
       <c r="U8" s="4" t="n"/>
       <c r="V8" s="4" t="n"/>
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n"/>
-      <c r="Y8" s="4" t="n"/>
+      <c r="Y8" s="5" t="inlineStr">
+        <is>
+          <t>https://kakaopage-tracker.vercel.app/ (웹툰 TOP 300)</t>
+        </is>
+      </c>
+      <c r="Z8" s="5" t="inlineStr">
+        <is>
+          <t>08/16 269위</t>
+        </is>
+      </c>
+      <c r="AA8" s="5" t="n"/>
+      <c r="AB8" s="5" t="n"/>
+      <c r="AC8" s="5" t="inlineStr">
+        <is>
+          <t>46742689</t>
+        </is>
+      </c>
+      <c r="AD8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -5063,7 +5314,11 @@
           <t>웹툰 &gt; 로판</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>#로맨스판타지 #회귀물 #암투물 #여주판타지 #환생물 #능글남 #왕족/귀족 #능력남 #계략남 #걸크러쉬 #무심녀 #정략결혼 #첫사랑 #운명</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>전체 이용가</t>
@@ -5108,14 +5363,53 @@
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>카카오페이지 웹소설 content/48068866 (원작: Unias)</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="n"/>
-      <c r="V9" s="4" t="n"/>
-      <c r="W9" s="4" t="n"/>
-      <c r="X9" s="4" t="n"/>
-      <c r="Y9" s="4" t="n"/>
+          <t>카카오페이지 웹소설 content/48068866 (동일작품 웹소설판 확인)</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="W9" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y9" s="5" t="inlineStr">
+        <is>
+          <t>https://kakaopage-tracker.vercel.app/ (웹툰 TOP 300)</t>
+        </is>
+      </c>
+      <c r="Z9" s="5" t="inlineStr">
+        <is>
+          <t>08/10 10위 · 08/11 1위 · 08/12 1위 · 08/13 2위 · 08/14 4위 · 08/15 13위 · 08/16 13위 · 08/17 34위 · 08/18 19위 · 08/19 13위 · 08/20 21위 · 08/21 39위</t>
+        </is>
+      </c>
+      <c r="AA9" s="5" t="inlineStr">
+        <is>
+          <t>08/10 49위 · 08/11 3위 · 08/12 1위 · 08/13 1위 · 08/14 1위 · 08/15 1위 · 08/16 1위 · 08/17 2위 · 08/18 6위 · 08/19 13위 · 08/20 21위 · 08/21 22위</t>
+        </is>
+      </c>
+      <c r="AB9" s="5" t="inlineStr">
+        <is>
+          <t>08/10 149위 · 08/11 33위 · 08/12 21위 · 08/13 16위 · 08/14 15위 · 08/15 15위 · 08/16 15위 · 08/17 15위 · 08/18 13위 · 08/19 11위 · 08/20 11위 · 08/21 10위</t>
+        </is>
+      </c>
+      <c r="AC9" s="5" t="inlineStr">
+        <is>
+          <t>48068866</t>
+        </is>
+      </c>
+      <c r="AD9" s="5" t="inlineStr">
+        <is>
+          <t>제이플미디어</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -5156,7 +5450,11 @@
           <t>웹툰 &gt; 로판</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>#로맨스판타지 #육아물 #환생물 #성장물 #가족물 #짝사랑 #순정남 #짝사랑남 #능력녀 #엉뚱발랄녀 #친구&gt;연인 #소꿉친구 #힐링물</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>전체 이용가</t>
@@ -5201,14 +5499,53 @@
       </c>
       <c r="T10" s="5" t="inlineStr">
         <is>
-          <t>카카오페이지 웹소설 content/62171261 (원작: 매드럼)</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="n"/>
-      <c r="V10" s="4" t="n"/>
-      <c r="W10" s="4" t="n"/>
-      <c r="X10" s="4" t="n"/>
-      <c r="Y10" s="4" t="n"/>
+          <t>카카오페이지 웹소설 content/62171261 (동일작품 웹소설판 확인)</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="W10" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="X10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Y10" s="5" t="inlineStr">
+        <is>
+          <t>https://kakaopage-tracker.vercel.app/ (웹툰 TOP 300)</t>
+        </is>
+      </c>
+      <c r="Z10" s="5" t="inlineStr">
+        <is>
+          <t>08/09 30위 · 08/10 11위 · 08/11 23위 · 08/12 48위 · 08/13 76위 · 08/14 91위 · 08/15 100위 · 08/16 71위 · 08/17 44위 · 08/18 69위 · 08/19 76위 · 08/20 93위 · 08/21 106위</t>
+        </is>
+      </c>
+      <c r="AA10" s="5" t="inlineStr">
+        <is>
+          <t>08/09 66위 · 08/10 43위 · 08/11 41위 · 08/12 40위 · 08/13 41위 · 08/14 40위 · 08/15 40위 · 08/16 45위 · 08/17 62위 · 08/18 76위 · 08/19 79위 · 08/20 78위 · 08/21 77위</t>
+        </is>
+      </c>
+      <c r="AB10" s="5" t="inlineStr">
+        <is>
+          <t>08/09 73위 · 08/10 68위 · 08/11 70위 · 08/12 77위 · 08/13 81위 · 08/14 83위 · 08/15 83위 · 08/16 83위 · 08/17 84위 · 08/18 84위 · 08/19 85위 · 08/20 83위 · 08/21 84위</t>
+        </is>
+      </c>
+      <c r="AC10" s="5" t="inlineStr">
+        <is>
+          <t>62171261</t>
+        </is>
+      </c>
+      <c r="AD10" s="5" t="inlineStr">
+        <is>
+          <t>곁beside / 위즈덤하우스</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -5249,7 +5586,11 @@
           <t>웹툰 &gt; 무협</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>#회귀 #마교 #정파 #천마 #퓨전 #성장 #먼치킨</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>전체 이용가</t>
@@ -5294,14 +5635,35 @@
       </c>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>카카오페이지 웹소설 content/64703609 (원작: 우바람)</t>
+          <t>카카오페이지 웹소설 content/64703609 (동일작품 웹소설판 확인)</t>
         </is>
       </c>
       <c r="U11" s="4" t="n"/>
       <c r="V11" s="4" t="n"/>
       <c r="W11" s="4" t="n"/>
       <c r="X11" s="4" t="n"/>
-      <c r="Y11" s="4" t="n"/>
+      <c r="Y11" s="5" t="inlineStr">
+        <is>
+          <t>https://kakaopage-tracker.vercel.app/ (웹툰 TOP 300)</t>
+        </is>
+      </c>
+      <c r="Z11" s="5" t="inlineStr">
+        <is>
+          <t>08/11 277위 · 08/12 273위</t>
+        </is>
+      </c>
+      <c r="AA11" s="5" t="n"/>
+      <c r="AB11" s="5" t="n"/>
+      <c r="AC11" s="5" t="inlineStr">
+        <is>
+          <t>64703609</t>
+        </is>
+      </c>
+      <c r="AD11" s="5" t="inlineStr">
+        <is>
+          <t>노벨피아</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -5342,7 +5704,11 @@
           <t>웹툰 &gt; 로판</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>#로맨스판타지 #육아물 #먼치킨 #성장물 #회귀물</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>전체 이용가</t>
@@ -5387,14 +5753,23 @@
       </c>
       <c r="T12" s="5" t="inlineStr">
         <is>
-          <t>카카오페이지 웹소설 content/57012392 (원작: 라비올리)</t>
+          <t>카카오페이지 웹소설 content/57012392 (동일작품 웹소설판 확인)</t>
         </is>
       </c>
       <c r="U12" s="4" t="n"/>
       <c r="V12" s="4" t="n"/>
       <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n"/>
-      <c r="Y12" s="4" t="n"/>
+      <c r="Y12" s="5" t="n"/>
+      <c r="Z12" s="5" t="n"/>
+      <c r="AA12" s="5" t="n"/>
+      <c r="AB12" s="5" t="n"/>
+      <c r="AC12" s="5" t="inlineStr">
+        <is>
+          <t>57012392</t>
+        </is>
+      </c>
+      <c r="AD12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -5487,7 +5862,12 @@
       <c r="V13" s="4" t="n"/>
       <c r="W13" s="4" t="n"/>
       <c r="X13" s="4" t="n"/>
-      <c r="Y13" s="4" t="n"/>
+      <c r="Y13" s="5" t="n"/>
+      <c r="Z13" s="5" t="n"/>
+      <c r="AA13" s="5" t="n"/>
+      <c r="AB13" s="5" t="n"/>
+      <c r="AC13" s="5" t="n"/>
+      <c r="AD13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -5528,7 +5908,11 @@
           <t>웹툰 &gt; 로판</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>#라이벌/앙숙 #사이다녀 #걸크러쉬 #능력녀 #회귀물 #로맨스판타지 #소유욕/독점욕 #능력남 #재회물 #기사물 #중세물 #여주판타지 #직진남</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>전체 이용가</t>
@@ -5573,14 +5957,35 @@
       </c>
       <c r="T14" s="5" t="inlineStr">
         <is>
-          <t>카카오페이지 웹소설 content/47674166 (원작: 혜돌이)</t>
+          <t>카카오페이지 웹소설 content/47674166 (동일작품 웹소설판 확인)</t>
         </is>
       </c>
       <c r="U14" s="4" t="n"/>
       <c r="V14" s="4" t="n"/>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n"/>
-      <c r="Y14" s="4" t="n"/>
+      <c r="Y14" s="5" t="inlineStr">
+        <is>
+          <t>https://kakaopage-tracker.vercel.app/ (웹툰 TOP 300)</t>
+        </is>
+      </c>
+      <c r="Z14" s="5" t="inlineStr">
+        <is>
+          <t>08/11 179위 · 08/18 180위 · 08/19 296위</t>
+        </is>
+      </c>
+      <c r="AA14" s="5" t="n"/>
+      <c r="AB14" s="5" t="n"/>
+      <c r="AC14" s="5" t="inlineStr">
+        <is>
+          <t>47674166</t>
+        </is>
+      </c>
+      <c r="AD14" s="5" t="inlineStr">
+        <is>
+          <t>미스터블루 주식회사 / 제로노블</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -5621,7 +6026,11 @@
           <t>웹툰 &gt; 로판</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>#로맨스판타지 #빙의물 #초월적존재 #계략남 #소유욕/독점욕 #집착남 #평범녀 #엉뚱발랄녀 #직진녀 #로맨틱코미디 #신분차이</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t>15세 이용가</t>
@@ -5666,14 +6075,39 @@
       </c>
       <c r="T15" s="5" t="inlineStr">
         <is>
-          <t>카카오페이지 웹소설 content/58146031 (원작: 김욤뇸)</t>
+          <t>카카오페이지 웹소설 content/58146031 (동일작품 웹소설판 확인)</t>
         </is>
       </c>
       <c r="U15" s="4" t="n"/>
       <c r="V15" s="4" t="n"/>
       <c r="W15" s="4" t="n"/>
       <c r="X15" s="4" t="n"/>
-      <c r="Y15" s="4" t="n"/>
+      <c r="Y15" s="5" t="inlineStr">
+        <is>
+          <t>https://kakaopage-tracker.vercel.app/ (웹툰 TOP 300)</t>
+        </is>
+      </c>
+      <c r="Z15" s="5" t="inlineStr">
+        <is>
+          <t>08/13 291위</t>
+        </is>
+      </c>
+      <c r="AA15" s="5" t="n"/>
+      <c r="AB15" s="5" t="inlineStr">
+        <is>
+          <t>08/09 241위 · 08/10 240위 · 08/11 293위</t>
+        </is>
+      </c>
+      <c r="AC15" s="5" t="inlineStr">
+        <is>
+          <t>58146031</t>
+        </is>
+      </c>
+      <c r="AD15" s="5" t="inlineStr">
+        <is>
+          <t>팝콘미디어 / 서커스</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -5714,7 +6148,11 @@
           <t>웹툰 &gt; 드라마</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>#추리물 #중세물 #영혼체인지/빙의 #초월적존재 #고퀄리티 #남주중심 #노블코믹 #왕족/귀족</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>전체 이용가</t>
@@ -5759,14 +6197,23 @@
       </c>
       <c r="T16" s="5" t="inlineStr">
         <is>
-          <t>작가 크레딧 "원작: 사이딘" (웹소설 페이지 미확인)</t>
+          <t>카카오페이지 웹소설 content/47218337 (동일작품 웹소설판 확인)</t>
         </is>
       </c>
       <c r="U16" s="4" t="n"/>
       <c r="V16" s="4" t="n"/>
       <c r="W16" s="4" t="n"/>
       <c r="X16" s="4" t="n"/>
-      <c r="Y16" s="4" t="n"/>
+      <c r="Y16" s="5" t="n"/>
+      <c r="Z16" s="5" t="n"/>
+      <c r="AA16" s="5" t="n"/>
+      <c r="AB16" s="5" t="n"/>
+      <c r="AC16" s="5" t="inlineStr">
+        <is>
+          <t>47218337</t>
+        </is>
+      </c>
+      <c r="AD16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -5859,7 +6306,12 @@
       <c r="V17" s="4" t="n"/>
       <c r="W17" s="4" t="n"/>
       <c r="X17" s="4" t="n"/>
-      <c r="Y17" s="4" t="n"/>
+      <c r="Y17" s="5" t="n"/>
+      <c r="Z17" s="5" t="n"/>
+      <c r="AA17" s="5" t="n"/>
+      <c r="AB17" s="5" t="n"/>
+      <c r="AC17" s="5" t="n"/>
+      <c r="AD17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -5900,7 +6352,11 @@
           <t>웹툰 &gt; 로판</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>#로맨스판타지 #빙의물 #여주판타지 #왕족/귀족 #철벽녀 #털털녀 #로맨틱코미디</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>전체 이용가</t>
@@ -5945,14 +6401,23 @@
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>작가 크레딧 "원작: 노희다"</t>
+          <t>카카오페이지 웹소설 content/50839443 (동일작품 웹소설판 확인)</t>
         </is>
       </c>
       <c r="U18" s="4" t="n"/>
       <c r="V18" s="4" t="n"/>
       <c r="W18" s="4" t="n"/>
       <c r="X18" s="4" t="n"/>
-      <c r="Y18" s="4" t="n"/>
+      <c r="Y18" s="5" t="n"/>
+      <c r="Z18" s="5" t="n"/>
+      <c r="AA18" s="5" t="n"/>
+      <c r="AB18" s="5" t="n"/>
+      <c r="AC18" s="5" t="inlineStr">
+        <is>
+          <t>50839443</t>
+        </is>
+      </c>
+      <c r="AD18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -5993,7 +6458,11 @@
           <t>웹툰 &gt; 판타지</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>#게임 #하렘 #학원 #먼치킨 #착각 #생존</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
           <t>15세 이용가</t>
@@ -6038,14 +6507,23 @@
       </c>
       <c r="T19" s="5" t="inlineStr">
         <is>
-          <t>작가 크레딧 "원작: 리틀빅"</t>
+          <t>카카오페이지 웹소설 content/64316403 (동일작품 웹소설판 확인)</t>
         </is>
       </c>
       <c r="U19" s="4" t="n"/>
       <c r="V19" s="4" t="n"/>
       <c r="W19" s="4" t="n"/>
       <c r="X19" s="4" t="n"/>
-      <c r="Y19" s="4" t="n"/>
+      <c r="Y19" s="5" t="n"/>
+      <c r="Z19" s="5" t="n"/>
+      <c r="AA19" s="5" t="n"/>
+      <c r="AB19" s="5" t="n"/>
+      <c r="AC19" s="5" t="inlineStr">
+        <is>
+          <t>64316403</t>
+        </is>
+      </c>
+      <c r="AD19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -6086,7 +6564,11 @@
           <t>웹툰 &gt; 판타지</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>#차원이동 #귀환 #먼치킨 #성장 #이능력 #네크로맨서</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>전체 이용가</t>
@@ -6131,14 +6613,23 @@
       </c>
       <c r="T20" s="5" t="inlineStr">
         <is>
-          <t>작가 크레딧 "원작: 소주귀신"</t>
+          <t>카카오페이지 웹소설 content/61244709 (동일작품 웹소설판 확인)</t>
         </is>
       </c>
       <c r="U20" s="4" t="n"/>
       <c r="V20" s="4" t="n"/>
       <c r="W20" s="4" t="n"/>
       <c r="X20" s="4" t="n"/>
-      <c r="Y20" s="4" t="n"/>
+      <c r="Y20" s="5" t="n"/>
+      <c r="Z20" s="5" t="n"/>
+      <c r="AA20" s="5" t="n"/>
+      <c r="AB20" s="5" t="n"/>
+      <c r="AC20" s="5" t="inlineStr">
+        <is>
+          <t>61244709</t>
+        </is>
+      </c>
+      <c r="AD20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -6231,7 +6722,12 @@
       <c r="V21" s="4" t="n"/>
       <c r="W21" s="4" t="n"/>
       <c r="X21" s="4" t="n"/>
-      <c r="Y21" s="4" t="n"/>
+      <c r="Y21" s="5" t="n"/>
+      <c r="Z21" s="5" t="n"/>
+      <c r="AA21" s="5" t="n"/>
+      <c r="AB21" s="5" t="n"/>
+      <c r="AC21" s="5" t="n"/>
+      <c r="AD21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -6324,7 +6820,12 @@
       <c r="V22" s="4" t="n"/>
       <c r="W22" s="4" t="n"/>
       <c r="X22" s="4" t="n"/>
-      <c r="Y22" s="4" t="n"/>
+      <c r="Y22" s="5" t="n"/>
+      <c r="Z22" s="5" t="n"/>
+      <c r="AA22" s="5" t="n"/>
+      <c r="AB22" s="5" t="n"/>
+      <c r="AC22" s="5" t="n"/>
+      <c r="AD22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -6417,7 +6918,12 @@
       <c r="V23" s="4" t="n"/>
       <c r="W23" s="4" t="n"/>
       <c r="X23" s="4" t="n"/>
-      <c r="Y23" s="4" t="n"/>
+      <c r="Y23" s="5" t="n"/>
+      <c r="Z23" s="5" t="n"/>
+      <c r="AA23" s="5" t="n"/>
+      <c r="AB23" s="5" t="n"/>
+      <c r="AC23" s="5" t="n"/>
+      <c r="AD23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -6510,7 +7016,12 @@
       <c r="V24" s="4" t="n"/>
       <c r="W24" s="4" t="n"/>
       <c r="X24" s="4" t="n"/>
-      <c r="Y24" s="4" t="n"/>
+      <c r="Y24" s="5" t="n"/>
+      <c r="Z24" s="5" t="n"/>
+      <c r="AA24" s="5" t="n"/>
+      <c r="AB24" s="5" t="n"/>
+      <c r="AC24" s="5" t="n"/>
+      <c r="AD24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -6603,7 +7114,12 @@
       <c r="V25" s="4" t="n"/>
       <c r="W25" s="4" t="n"/>
       <c r="X25" s="4" t="n"/>
-      <c r="Y25" s="4" t="n"/>
+      <c r="Y25" s="5" t="n"/>
+      <c r="Z25" s="5" t="n"/>
+      <c r="AA25" s="5" t="n"/>
+      <c r="AB25" s="5" t="n"/>
+      <c r="AC25" s="5" t="n"/>
+      <c r="AD25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -6696,7 +7212,12 @@
       <c r="V26" s="4" t="n"/>
       <c r="W26" s="4" t="n"/>
       <c r="X26" s="4" t="n"/>
-      <c r="Y26" s="4" t="n"/>
+      <c r="Y26" s="5" t="n"/>
+      <c r="Z26" s="5" t="n"/>
+      <c r="AA26" s="5" t="n"/>
+      <c r="AB26" s="5" t="n"/>
+      <c r="AC26" s="5" t="n"/>
+      <c r="AD26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -6789,7 +7310,12 @@
       <c r="V27" s="4" t="n"/>
       <c r="W27" s="4" t="n"/>
       <c r="X27" s="4" t="n"/>
-      <c r="Y27" s="4" t="n"/>
+      <c r="Y27" s="5" t="n"/>
+      <c r="Z27" s="5" t="n"/>
+      <c r="AA27" s="5" t="n"/>
+      <c r="AB27" s="5" t="n"/>
+      <c r="AC27" s="5" t="n"/>
+      <c r="AD27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -6882,7 +7408,12 @@
       <c r="V28" s="4" t="n"/>
       <c r="W28" s="4" t="n"/>
       <c r="X28" s="4" t="n"/>
-      <c r="Y28" s="4" t="n"/>
+      <c r="Y28" s="5" t="n"/>
+      <c r="Z28" s="5" t="n"/>
+      <c r="AA28" s="5" t="n"/>
+      <c r="AB28" s="5" t="n"/>
+      <c r="AC28" s="5" t="n"/>
+      <c r="AD28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -6975,7 +7506,12 @@
       <c r="V29" s="4" t="n"/>
       <c r="W29" s="4" t="n"/>
       <c r="X29" s="4" t="n"/>
-      <c r="Y29" s="4" t="n"/>
+      <c r="Y29" s="5" t="n"/>
+      <c r="Z29" s="5" t="n"/>
+      <c r="AA29" s="5" t="n"/>
+      <c r="AB29" s="5" t="n"/>
+      <c r="AC29" s="5" t="n"/>
+      <c r="AD29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -7068,7 +7604,12 @@
       <c r="V30" s="4" t="n"/>
       <c r="W30" s="4" t="n"/>
       <c r="X30" s="4" t="n"/>
-      <c r="Y30" s="4" t="n"/>
+      <c r="Y30" s="5" t="n"/>
+      <c r="Z30" s="5" t="n"/>
+      <c r="AA30" s="5" t="n"/>
+      <c r="AB30" s="5" t="n"/>
+      <c r="AC30" s="5" t="n"/>
+      <c r="AD30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -7161,7 +7702,12 @@
       <c r="V31" s="4" t="n"/>
       <c r="W31" s="4" t="n"/>
       <c r="X31" s="4" t="n"/>
-      <c r="Y31" s="4" t="n"/>
+      <c r="Y31" s="5" t="n"/>
+      <c r="Z31" s="5" t="n"/>
+      <c r="AA31" s="5" t="n"/>
+      <c r="AB31" s="5" t="n"/>
+      <c r="AC31" s="5" t="n"/>
+      <c r="AD31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -7254,7 +7800,12 @@
       <c r="V32" s="4" t="n"/>
       <c r="W32" s="4" t="n"/>
       <c r="X32" s="4" t="n"/>
-      <c r="Y32" s="4" t="n"/>
+      <c r="Y32" s="5" t="n"/>
+      <c r="Z32" s="5" t="n"/>
+      <c r="AA32" s="5" t="n"/>
+      <c r="AB32" s="5" t="n"/>
+      <c r="AC32" s="5" t="n"/>
+      <c r="AD32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -7295,7 +7846,11 @@
           <t>웹툰 &gt; 로맨스</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>#동양풍 #복수물 #소유욕/독점욕 #왕족/귀족 #외유내강 #털털녀 #가상시대물 #운명 #오만남 #능글남 #엉뚱발랄녀 #능력녀 #신분차이 #달달물</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>15세 이용가</t>
@@ -7340,14 +7895,23 @@
       </c>
       <c r="T33" s="5" t="inlineStr">
         <is>
-          <t>카카오페이지 웹소설 content/50741989 (원작: 솔땀)</t>
+          <t>카카오페이지 웹소설 content/50741989 (동일작품 웹소설판 확인)</t>
         </is>
       </c>
       <c r="U33" s="4" t="n"/>
       <c r="V33" s="4" t="n"/>
       <c r="W33" s="4" t="n"/>
       <c r="X33" s="4" t="n"/>
-      <c r="Y33" s="4" t="n"/>
+      <c r="Y33" s="5" t="n"/>
+      <c r="Z33" s="5" t="n"/>
+      <c r="AA33" s="5" t="n"/>
+      <c r="AB33" s="5" t="n"/>
+      <c r="AC33" s="5" t="inlineStr">
+        <is>
+          <t>50741989</t>
+        </is>
+      </c>
+      <c r="AD33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -7440,7 +8004,12 @@
       <c r="V34" s="4" t="n"/>
       <c r="W34" s="4" t="n"/>
       <c r="X34" s="4" t="n"/>
-      <c r="Y34" s="4" t="n"/>
+      <c r="Y34" s="5" t="n"/>
+      <c r="Z34" s="5" t="n"/>
+      <c r="AA34" s="5" t="n"/>
+      <c r="AB34" s="5" t="n"/>
+      <c r="AC34" s="5" t="n"/>
+      <c r="AD34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -7533,7 +8102,12 @@
       <c r="V35" s="4" t="n"/>
       <c r="W35" s="4" t="n"/>
       <c r="X35" s="4" t="n"/>
-      <c r="Y35" s="4" t="n"/>
+      <c r="Y35" s="5" t="n"/>
+      <c r="Z35" s="5" t="n"/>
+      <c r="AA35" s="5" t="n"/>
+      <c r="AB35" s="5" t="n"/>
+      <c r="AC35" s="5" t="n"/>
+      <c r="AD35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -7626,7 +8200,12 @@
       <c r="V36" s="4" t="n"/>
       <c r="W36" s="4" t="n"/>
       <c r="X36" s="4" t="n"/>
-      <c r="Y36" s="4" t="n"/>
+      <c r="Y36" s="5" t="n"/>
+      <c r="Z36" s="5" t="n"/>
+      <c r="AA36" s="5" t="n"/>
+      <c r="AB36" s="5" t="n"/>
+      <c r="AC36" s="5" t="n"/>
+      <c r="AD36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -7719,7 +8298,12 @@
       <c r="V37" s="4" t="n"/>
       <c r="W37" s="4" t="n"/>
       <c r="X37" s="4" t="n"/>
-      <c r="Y37" s="4" t="n"/>
+      <c r="Y37" s="5" t="n"/>
+      <c r="Z37" s="5" t="n"/>
+      <c r="AA37" s="5" t="n"/>
+      <c r="AB37" s="5" t="n"/>
+      <c r="AC37" s="5" t="n"/>
+      <c r="AD37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -7812,7 +8396,12 @@
       <c r="V38" s="4" t="n"/>
       <c r="W38" s="4" t="n"/>
       <c r="X38" s="4" t="n"/>
-      <c r="Y38" s="4" t="n"/>
+      <c r="Y38" s="5" t="n"/>
+      <c r="Z38" s="5" t="n"/>
+      <c r="AA38" s="5" t="n"/>
+      <c r="AB38" s="5" t="n"/>
+      <c r="AC38" s="5" t="n"/>
+      <c r="AD38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -7905,7 +8494,12 @@
       <c r="V39" s="4" t="n"/>
       <c r="W39" s="4" t="n"/>
       <c r="X39" s="4" t="n"/>
-      <c r="Y39" s="4" t="n"/>
+      <c r="Y39" s="5" t="n"/>
+      <c r="Z39" s="5" t="n"/>
+      <c r="AA39" s="5" t="n"/>
+      <c r="AB39" s="5" t="n"/>
+      <c r="AC39" s="5" t="n"/>
+      <c r="AD39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -7946,7 +8540,11 @@
           <t>웹툰 &gt; 로맨스</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>#현대로맨스 #동거물 #성장물 #인외존재 #역하렘 #능력남 #존댓말남 #다정남 #엉뚱발랄녀 #외유내강 #힐링물</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
           <t>전체 이용가</t>
@@ -7987,14 +8585,19 @@
       </c>
       <c r="T40" s="5" t="inlineStr">
         <is>
-          <t>웹툰 오리지널 (네이버웹툰 연재작, 원작 크레딧 없음)</t>
+          <t>카카오페이지 동일작품 웹소설판 없음 (웹툰 오리지널)</t>
         </is>
       </c>
       <c r="U40" s="4" t="n"/>
       <c r="V40" s="4" t="n"/>
       <c r="W40" s="4" t="n"/>
       <c r="X40" s="4" t="n"/>
-      <c r="Y40" s="4" t="n"/>
+      <c r="Y40" s="5" t="n"/>
+      <c r="Z40" s="5" t="n"/>
+      <c r="AA40" s="5" t="n"/>
+      <c r="AB40" s="5" t="n"/>
+      <c r="AC40" s="5" t="n"/>
+      <c r="AD40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -8083,7 +8686,12 @@
       <c r="V41" s="4" t="n"/>
       <c r="W41" s="4" t="n"/>
       <c r="X41" s="4" t="n"/>
-      <c r="Y41" s="4" t="n"/>
+      <c r="Y41" s="5" t="n"/>
+      <c r="Z41" s="5" t="n"/>
+      <c r="AA41" s="5" t="n"/>
+      <c r="AB41" s="5" t="n"/>
+      <c r="AC41" s="5" t="n"/>
+      <c r="AD41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -8172,7 +8780,12 @@
       <c r="V42" s="4" t="n"/>
       <c r="W42" s="4" t="n"/>
       <c r="X42" s="4" t="n"/>
-      <c r="Y42" s="4" t="n"/>
+      <c r="Y42" s="5" t="n"/>
+      <c r="Z42" s="5" t="n"/>
+      <c r="AA42" s="5" t="n"/>
+      <c r="AB42" s="5" t="n"/>
+      <c r="AC42" s="5" t="n"/>
+      <c r="AD42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -8261,7 +8874,12 @@
       <c r="V43" s="4" t="n"/>
       <c r="W43" s="4" t="n"/>
       <c r="X43" s="4" t="n"/>
-      <c r="Y43" s="4" t="n"/>
+      <c r="Y43" s="5" t="n"/>
+      <c r="Z43" s="5" t="n"/>
+      <c r="AA43" s="5" t="n"/>
+      <c r="AB43" s="5" t="n"/>
+      <c r="AC43" s="5" t="n"/>
+      <c r="AD43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -8350,7 +8968,12 @@
       <c r="V44" s="4" t="n"/>
       <c r="W44" s="4" t="n"/>
       <c r="X44" s="4" t="n"/>
-      <c r="Y44" s="4" t="n"/>
+      <c r="Y44" s="5" t="n"/>
+      <c r="Z44" s="5" t="n"/>
+      <c r="AA44" s="5" t="n"/>
+      <c r="AB44" s="5" t="n"/>
+      <c r="AC44" s="5" t="n"/>
+      <c r="AD44" s="5" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R44"/>

--- a/디씨씨이엔티_연재처별_작품현황.xlsx
+++ b/디씨씨이엔티_연재처별_작품현황.xlsx
@@ -236,7 +236,8 @@
     <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t>원작 웹소설의 출판사(CP).
-카카오페이지 웹소설판이 트래커에 함께 수록된 건만 확보되어 있고, 나머지는 공백입니다.</t>
+근거는 AE열 참조 - 카카오페이지 웹소설 상세 또는 서점 판매목록(저자|출판사 표기)으로 확인된 건만 기입했습니다.
+확인되지 않은 건은 추정하지 않고 공백으로 두었습니다.</t>
       </text>
     </comment>
   </commentList>
@@ -4170,6 +4171,7 @@
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="3" t="inlineStr"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -4186,7 +4188,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>네트워크 정책상 차단 - 카카오페이지 키워드/태그 수집 불가</t>
+          <t>직접 수집 실패 - HTML은 열리나 클라이언트 렌더링이고 GraphQL은 카카오 봇차단(403). 태그는 트래커 works.json(카카오페이지 수집분) 19건으로 대체</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4212,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>검색 및 작가 크레딧 기반 판정 완료 (기준일 2026-08-20, 근거는 카카오페이지 시트 T열)</t>
+          <t>43건 판정 완료(O 36 / X 7). 이 중 19건은 카카오페이지 동일작품 웹소설판으로 확정, 출판사 20건 확보(근거 AE열). 리디 교차확인은 Cloudflare 봇차단으로 불가</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD44"/>
+  <dimension ref="A1:AE44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4259,6 +4261,7 @@
     <col width="52" customWidth="1" min="28" max="28"/>
     <col width="14" customWidth="1" min="29" max="29"/>
     <col width="30" customWidth="1" min="30" max="30"/>
+    <col width="52" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4412,6 +4415,11 @@
           <t>웹소설 출판사</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>출판사 확인 근거</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -4546,6 +4554,11 @@
           <t>브리드 / A-LIST</t>
         </is>
       </c>
+      <c r="AE2" s="5" t="inlineStr">
+        <is>
+          <t>카카오페이지 웹소설 상세 (트래커 works.json)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -4678,6 +4691,11 @@
       <c r="AD3" s="5" t="inlineStr">
         <is>
           <t>제이플미디어</t>
+        </is>
+      </c>
+      <c r="AE3" s="5" t="inlineStr">
+        <is>
+          <t>카카오페이지 웹소설 상세 (트래커 works.json)</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4939,16 @@
           <t>63949783</t>
         </is>
       </c>
-      <c r="AD5" s="5" t="n"/>
+      <c r="AD5" s="5" t="inlineStr">
+        <is>
+          <t>노벨피아</t>
+        </is>
+      </c>
+      <c r="AE5" s="5" t="inlineStr">
+        <is>
+          <t>예스24 [세트] 아싸 찐따 네크로맨서(총7권/완결) | 신채화 | 노벨피아</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -5027,7 +5054,16 @@
           <t>56203718</t>
         </is>
       </c>
-      <c r="AD6" s="5" t="n"/>
+      <c r="AD6" s="5" t="inlineStr">
+        <is>
+          <t>동아</t>
+        </is>
+      </c>
+      <c r="AE6" s="5" t="inlineStr">
+        <is>
+          <t>예스24 선 넘는 로맨스 | 민지안 | 동아</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -5410,6 +5446,11 @@
           <t>제이플미디어</t>
         </is>
       </c>
+      <c r="AE9" s="5" t="inlineStr">
+        <is>
+          <t>카카오페이지 웹소설 상세 (트래커 works.json)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -5544,6 +5585,11 @@
       <c r="AD10" s="5" t="inlineStr">
         <is>
           <t>곁beside / 위즈덤하우스</t>
+        </is>
+      </c>
+      <c r="AE10" s="5" t="inlineStr">
+        <is>
+          <t>카카오페이지 웹소설 상세 (트래커 works.json)</t>
         </is>
       </c>
     </row>
@@ -5662,6 +5708,11 @@
       <c r="AD11" s="5" t="inlineStr">
         <is>
           <t>노벨피아</t>
+        </is>
+      </c>
+      <c r="AE11" s="5" t="inlineStr">
+        <is>
+          <t>카카오페이지 웹소설 상세 (트래커 works.json)</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5820,16 @@
           <t>57012392</t>
         </is>
       </c>
-      <c r="AD12" s="5" t="n"/>
+      <c r="AD12" s="5" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="AE12" s="5" t="inlineStr">
+        <is>
+          <t>예스24 전생의 원수가 아빠라고요? | 라비올리 | MALANG</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -5855,7 +5915,7 @@
       </c>
       <c r="T13" s="5" t="inlineStr">
         <is>
-          <t>카카오페이지 웹소설 content/60558550 (원작: 김차차)</t>
+          <t>카카오페이지 웹소설 content/60558545 (이 결혼은 어차피 망하게 되어 있다 [19세 완전판])</t>
         </is>
       </c>
       <c r="U13" s="4" t="n"/>
@@ -5866,7 +5926,11 @@
       <c r="Z13" s="5" t="n"/>
       <c r="AA13" s="5" t="n"/>
       <c r="AB13" s="5" t="n"/>
-      <c r="AC13" s="5" t="n"/>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>60558545</t>
+        </is>
+      </c>
       <c r="AD13" s="5" t="n"/>
     </row>
     <row r="14">
@@ -5986,6 +6050,11 @@
           <t>미스터블루 주식회사 / 제로노블</t>
         </is>
       </c>
+      <c r="AE14" s="5" t="inlineStr">
+        <is>
+          <t>카카오페이지 웹소설 상세 (트래커 works.json)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -6106,6 +6175,11 @@
       <c r="AD15" s="5" t="inlineStr">
         <is>
           <t>팝콘미디어 / 서커스</t>
+        </is>
+      </c>
+      <c r="AE15" s="5" t="inlineStr">
+        <is>
+          <t>카카오페이지 웹소설 상세 (트래커 works.json)</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6385,16 @@
       <c r="AA17" s="5" t="n"/>
       <c r="AB17" s="5" t="n"/>
       <c r="AC17" s="5" t="n"/>
-      <c r="AD17" s="5" t="n"/>
+      <c r="AD17" s="5" t="inlineStr">
+        <is>
+          <t>블라썸</t>
+        </is>
+      </c>
+      <c r="AE17" s="5" t="inlineStr">
+        <is>
+          <t>예스24 [세트] 닭장 속 공주님(총4권/완결) | 이미은 | 블라썸</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -6417,7 +6500,16 @@
           <t>50839443</t>
         </is>
       </c>
-      <c r="AD18" s="5" t="n"/>
+      <c r="AD18" s="5" t="inlineStr">
+        <is>
+          <t>연담</t>
+        </is>
+      </c>
+      <c r="AE18" s="5" t="inlineStr">
+        <is>
+          <t>예스24 다행인지 불행인지 3권 | 노희다 | 연담</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -6523,7 +6615,16 @@
           <t>64316403</t>
         </is>
       </c>
-      <c r="AD19" s="5" t="n"/>
+      <c r="AD19" s="5" t="inlineStr">
+        <is>
+          <t>안타르티카(노벨피아)</t>
+        </is>
+      </c>
+      <c r="AE19" s="5" t="inlineStr">
+        <is>
+          <t>예스24 악당에게 사랑받는 운명입니다 14권(완결) | 리틀빅 | 안타르티카(노벨피아)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -6629,7 +6730,16 @@
           <t>61244709</t>
         </is>
       </c>
-      <c r="AD20" s="5" t="n"/>
+      <c r="AD20" s="5" t="inlineStr">
+        <is>
+          <t>제이플러스</t>
+        </is>
+      </c>
+      <c r="AE20" s="5" t="inlineStr">
+        <is>
+          <t>예스24 [세트] 재앙급 네크로맨서가 은퇴하는 법(총12권/완결) | 소주귀신 | 제이플러스</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -6923,7 +7033,16 @@
       <c r="AA23" s="5" t="n"/>
       <c r="AB23" s="5" t="n"/>
       <c r="AC23" s="5" t="n"/>
-      <c r="AD23" s="5" t="n"/>
+      <c r="AD23" s="5" t="inlineStr">
+        <is>
+          <t>가하 에픽</t>
+        </is>
+      </c>
+      <c r="AE23" s="5" t="inlineStr">
+        <is>
+          <t>교보ebook 밤은 두 개의 이름을 가지고 있다 2 | 한하연 | 가하 에픽</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -7119,7 +7238,16 @@
       <c r="AA25" s="5" t="n"/>
       <c r="AB25" s="5" t="n"/>
       <c r="AC25" s="5" t="n"/>
-      <c r="AD25" s="5" t="n"/>
+      <c r="AD25" s="5" t="inlineStr">
+        <is>
+          <t>페리윙클</t>
+        </is>
+      </c>
+      <c r="AE25" s="5" t="inlineStr">
+        <is>
+          <t>예스24 이번 생은 제대로 키워 드리겠습니다, 폐하! 2권 | 자하 | 페리윙클</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -7217,7 +7345,16 @@
       <c r="AA26" s="5" t="n"/>
       <c r="AB26" s="5" t="n"/>
       <c r="AC26" s="5" t="n"/>
-      <c r="AD26" s="5" t="n"/>
+      <c r="AD26" s="5" t="inlineStr">
+        <is>
+          <t>러브홀릭</t>
+        </is>
+      </c>
+      <c r="AE26" s="5" t="inlineStr">
+        <is>
+          <t>예스24 엉큼한 맞선 1권 | 강영주 | 러브홀릭</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -7609,7 +7746,16 @@
       <c r="AA30" s="5" t="n"/>
       <c r="AB30" s="5" t="n"/>
       <c r="AC30" s="5" t="n"/>
-      <c r="AD30" s="5" t="n"/>
+      <c r="AD30" s="5" t="inlineStr">
+        <is>
+          <t>연담</t>
+        </is>
+      </c>
+      <c r="AE30" s="5" t="inlineStr">
+        <is>
+          <t>예스24 [세트] 악녀가 사랑할 때(총5권/완결) | 서귀조 | 연담</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -7707,7 +7853,16 @@
       <c r="AA31" s="5" t="n"/>
       <c r="AB31" s="5" t="n"/>
       <c r="AC31" s="5" t="n"/>
-      <c r="AD31" s="5" t="n"/>
+      <c r="AD31" s="5" t="inlineStr">
+        <is>
+          <t>CL프로덕션</t>
+        </is>
+      </c>
+      <c r="AE31" s="5" t="inlineStr">
+        <is>
+          <t>예스24 [세트] 왕의 딸로 태어났다고 합니다(총11권/완결) | 비츄 | CL프로덕션</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -8303,7 +8458,16 @@
       <c r="AA37" s="5" t="n"/>
       <c r="AB37" s="5" t="n"/>
       <c r="AC37" s="5" t="n"/>
-      <c r="AD37" s="5" t="n"/>
+      <c r="AD37" s="5" t="inlineStr">
+        <is>
+          <t>루시앤</t>
+        </is>
+      </c>
+      <c r="AE37" s="5" t="inlineStr">
+        <is>
+          <t>교보ebook 나를 찌르는 가시 | 마셰리 | 루시앤</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
